--- a/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Sep2026-Jun2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Sep2026-Jun2027.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sep 2026" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Oct 2026" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Nov 2026" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Dec 2026" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Jan 2027" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Feb 2027" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Mar 2027" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Apr 2027" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="May 2027" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Jun 2027" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sep 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oct 2026" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nov 2026" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dec 2026" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jan 2027" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feb 2027" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mar 2027" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apr 2027" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May 2027" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jun 2027" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4676,12 +4676,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>BRONSON, FARZEELA</t>
+          <t>MACNEILLE, FARZEELA</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE, FARZEELA</t>
+          <t>BRONSON, FARZEELA</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE, BRONSON</t>
+          <t>BRONSON, MACNEILLE</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
